--- a/School_docs/Premchand Mahto Inter College/Science/session 2026-28 science.xlsx
+++ b/School_docs/Premchand Mahto Inter College/Science/session 2026-28 science.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="89">
   <si>
     <t>ROLL NO.</t>
   </si>
@@ -193,6 +193,96 @@
   </si>
   <si>
     <t>PASSING  %</t>
+  </si>
+  <si>
+    <t>PREM KUMAR SAHU</t>
+  </si>
+  <si>
+    <t>ARJUN SAHU</t>
+  </si>
+  <si>
+    <t>MANJU DEVI</t>
+  </si>
+  <si>
+    <t>SAHIL RAJ</t>
+  </si>
+  <si>
+    <t>ONKAR KUMAR SINGH</t>
+  </si>
+  <si>
+    <t>GURIYA SINGH</t>
+  </si>
+  <si>
+    <t>PRITHVI KUMAR SINGH</t>
+  </si>
+  <si>
+    <t>SANTOSH KUMAR SINGH</t>
+  </si>
+  <si>
+    <t>PUNITA DEVI</t>
+  </si>
+  <si>
+    <t>ANKIT KUMAR SINGH</t>
+  </si>
+  <si>
+    <t>MAHESH SINGH</t>
+  </si>
+  <si>
+    <t>PHULWANTI DEVI</t>
+  </si>
+  <si>
+    <t>CHHOTU KUMAR</t>
+  </si>
+  <si>
+    <t>LT. SUDESH SINGH</t>
+  </si>
+  <si>
+    <t>SABITA DEVI</t>
+  </si>
+  <si>
+    <t>SHIFA KASHISH</t>
+  </si>
+  <si>
+    <t>KARIM ANSARI</t>
+  </si>
+  <si>
+    <t>SHAHNAJ KHATUN</t>
+  </si>
+  <si>
+    <t>ARIFA FALAK</t>
+  </si>
+  <si>
+    <t>MOHAMMAD ANSARI</t>
+  </si>
+  <si>
+    <t>NASIHA KHATOON</t>
+  </si>
+  <si>
+    <t>PIYUSH KUMAR</t>
+  </si>
+  <si>
+    <t>PRAMOD PASWAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JAC </t>
+  </si>
+  <si>
+    <t>MARUF ANSARI</t>
+  </si>
+  <si>
+    <t>MAHFUJ ANSARI</t>
+  </si>
+  <si>
+    <t>JAINAF KHATOON</t>
+  </si>
+  <si>
+    <t>SUMIT KUMAR SINGH</t>
+  </si>
+  <si>
+    <t>KAMTA SINGH</t>
+  </si>
+  <si>
+    <t>RINA DEVI</t>
   </si>
 </sst>
 </file>
@@ -554,7 +644,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
@@ -1035,6 +1125,305 @@
       </c>
       <c r="K16" s="1">
         <v>55.6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E17" s="4">
+        <v>39918</v>
+      </c>
+      <c r="G17" s="1">
+        <v>9534089123</v>
+      </c>
+      <c r="H17" s="6">
+        <v>236543687918</v>
+      </c>
+      <c r="I17" s="6">
+        <v>858488691773</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K17" s="1">
+        <v>99.6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E18" s="4">
+        <v>40449</v>
+      </c>
+      <c r="G18" s="1">
+        <v>7360066196</v>
+      </c>
+      <c r="H18" s="6">
+        <v>894533976172</v>
+      </c>
+      <c r="I18" s="6">
+        <v>594423851975</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E19" s="4">
+        <v>40419</v>
+      </c>
+      <c r="G19" s="1">
+        <v>9122713499</v>
+      </c>
+      <c r="H19" s="6">
+        <v>346392910724</v>
+      </c>
+      <c r="I19" s="6">
+        <v>572503063538</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E20" s="4">
+        <v>40145</v>
+      </c>
+      <c r="G20" s="1">
+        <v>9934649305</v>
+      </c>
+      <c r="H20" s="6">
+        <v>975930516879</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="K20" s="1">
+        <v>65.599999999999994</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E21" s="4">
+        <v>40522</v>
+      </c>
+      <c r="G21" s="1">
+        <v>7061232572</v>
+      </c>
+      <c r="H21" s="6">
+        <v>237706184326</v>
+      </c>
+      <c r="I21" s="6">
+        <v>735061241660</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E22" s="4">
+        <v>40354</v>
+      </c>
+      <c r="G22" s="1">
+        <v>8252364429</v>
+      </c>
+      <c r="H22" s="6">
+        <v>634570249982</v>
+      </c>
+      <c r="I22" s="6">
+        <v>425247505715</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" s="1">
+        <v>22</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E23" s="4">
+        <v>40277</v>
+      </c>
+      <c r="G23" s="1">
+        <v>9229646945</v>
+      </c>
+      <c r="H23" s="6">
+        <v>366238439847</v>
+      </c>
+      <c r="I23" s="6">
+        <v>963073664046</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K23" s="1">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" s="1">
+        <v>23</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E24" s="4">
+        <v>39814</v>
+      </c>
+      <c r="G24" s="1">
+        <v>6552232472</v>
+      </c>
+      <c r="H24" s="6">
+        <v>278527243962</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K24" s="1">
+        <v>70.8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" s="1">
+        <v>24</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E25" s="4">
+        <v>39547</v>
+      </c>
+      <c r="G25" s="1">
+        <v>6207084728</v>
+      </c>
+      <c r="H25" s="6">
+        <v>566889583104</v>
+      </c>
+      <c r="I25" s="6">
+        <v>876069854617</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K25" s="1">
+        <v>52.4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" s="1">
+        <v>25</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E26" s="4">
+        <v>40612</v>
+      </c>
+      <c r="G26" s="1">
+        <v>9229056266</v>
+      </c>
+      <c r="H26" s="6">
+        <v>540481222686</v>
+      </c>
+      <c r="I26" s="6">
+        <v>326868707671</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
